--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -179,24 +179,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
     <t>Martínez Cruz Norma</t>
   </si>
   <si>
-    <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,18 +209,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
     <t>ALCANTARA</t>
   </si>
   <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -233,9 +263,6 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>DEGANTE</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -251,9 +278,6 @@
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -275,9 +299,6 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SERRANO</t>
   </si>
   <si>
@@ -305,9 +326,6 @@
     <t>OLMOS</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>SEGURA</t>
   </si>
   <si>
@@ -320,9 +338,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
@@ -341,9 +356,6 @@
     <t>ROQUE</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
     <t>BERNAL</t>
   </si>
   <si>
@@ -383,12 +395,6 @@
     <t>IRIDIA</t>
   </si>
   <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
     <t>BRENDA JANET</t>
   </si>
   <si>
@@ -401,9 +407,6 @@
     <t>YOZELIN</t>
   </si>
   <si>
-    <t>SHARITH</t>
-  </si>
-  <si>
     <t>JHOVANA</t>
   </si>
   <si>
@@ -420,9 +423,6 @@
   </si>
   <si>
     <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
   </si>
   <si>
     <t>DIEGO OLLIN</t>
@@ -953,7 +953,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>10</v>
@@ -962,10 +962,10 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1016,10 +1016,10 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1030,7 +1030,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1039,10 +1039,10 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -1093,10 +1093,10 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1107,7 +1107,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1116,10 +1116,10 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1170,10 +1170,10 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -1193,10 +1193,10 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1247,10 +1247,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1270,10 +1270,10 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -1315,7 +1315,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1324,10 +1324,10 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1338,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -1347,10 +1347,10 @@
         <v>9</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1401,10 +1401,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1415,7 +1415,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1424,10 +1424,10 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>8</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1478,10 +1478,10 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1492,16 +1492,16 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>8</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1537,16 +1537,16 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1598,7 +1598,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1607,10 +1607,10 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -1652,7 +1652,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1661,10 +1661,10 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1675,7 +1675,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1684,10 +1684,10 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1729,7 +1729,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1738,10 +1738,10 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1752,7 +1752,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -1761,10 +1761,10 @@
         <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1806,7 +1806,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1815,10 +1815,10 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1829,7 +1829,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -1838,10 +1838,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1883,7 +1883,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -1892,10 +1892,10 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1906,7 +1906,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -1915,10 +1915,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>9</v>
@@ -1960,7 +1960,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1969,10 +1969,10 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1983,7 +1983,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -1992,10 +1992,10 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G18">
         <v>6</v>
@@ -2037,7 +2037,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2046,10 +2046,10 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2060,7 +2060,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2069,10 +2069,10 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -2114,7 +2114,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2123,10 +2123,10 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2137,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -2146,10 +2146,10 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -2191,7 +2191,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2200,10 +2200,10 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2214,7 +2214,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -2223,10 +2223,10 @@
         <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -2268,7 +2268,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2277,10 +2277,10 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2291,7 +2291,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>9</v>
@@ -2300,10 +2300,10 @@
         <v>8</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2345,7 +2345,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2354,10 +2354,10 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2368,7 +2368,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -2377,10 +2377,10 @@
         <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>7</v>
@@ -2422,7 +2422,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2431,10 +2431,10 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2445,7 +2445,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2454,10 +2454,10 @@
         <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G24">
         <v>9</v>
@@ -2499,7 +2499,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2508,10 +2508,10 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2522,7 +2522,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -2531,10 +2531,10 @@
         <v>8</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>9</v>
@@ -2576,7 +2576,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2585,10 +2585,10 @@
         <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2599,7 +2599,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -2608,10 +2608,10 @@
         <v>9</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>7</v>
@@ -2653,7 +2653,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2662,10 +2662,10 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2676,7 +2676,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>10</v>
@@ -2685,10 +2685,10 @@
         <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -2730,7 +2730,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2739,10 +2739,10 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2753,7 +2753,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -2762,10 +2762,10 @@
         <v>7</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2807,7 +2807,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2816,10 +2816,10 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2830,7 +2830,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -2839,10 +2839,10 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>8</v>
@@ -2884,7 +2884,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2893,10 +2893,10 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -2907,7 +2907,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C30">
         <v>8</v>
@@ -2916,10 +2916,10 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -2961,7 +2961,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2970,10 +2970,10 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -2984,7 +2984,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>10</v>
@@ -2993,10 +2993,10 @@
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>7</v>
@@ -3038,7 +3038,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -3047,10 +3047,10 @@
         <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3061,7 +3061,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -3070,10 +3070,10 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>7</v>
@@ -3115,7 +3115,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3124,10 +3124,10 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3138,7 +3138,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -3147,10 +3147,10 @@
         <v>10</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>8</v>
@@ -3192,7 +3192,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3201,10 +3201,10 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3215,7 +3215,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -3224,10 +3224,10 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G34">
         <v>6</v>
@@ -3269,7 +3269,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3278,10 +3278,10 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>6</v>
@@ -3292,7 +3292,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>10</v>
@@ -3301,10 +3301,10 @@
         <v>9</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>9</v>
@@ -3346,7 +3346,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3355,10 +3355,10 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3417,7 +3417,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3426,138 +3426,147 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>77.42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>19.35</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>87.5</v>
+      </c>
+      <c r="G3">
+        <v>12.5</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="E3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>31</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>7.6</v>
+      </c>
       <c r="I4">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
         <v>31</v>
       </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>77.42</v>
+        <v>96.88</v>
       </c>
       <c r="G5">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3568,7 +3577,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3577,25 +3586,25 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3605,7 +3614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3634,1961 +3643,101 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920270</v>
+        <v>19330051920269</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920270</v>
+        <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920270</v>
+        <v>18330051920319</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920272</v>
+        <v>18330051920319</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920272</v>
+        <v>19330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920272</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920269</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920269</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920269</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920269</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920273</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920273</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920273</v>
-      </c>
-      <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920273</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920268</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920268</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920268</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920274</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920274</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920274</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>18330051920242</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>18330051920242</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>18330051920242</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>17330051420245</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>17330051420245</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>17330051420245</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>18330051920319</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>18330051920319</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>18330051920321</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>18330051920321</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>18330051920321</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920278</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" t="s">
-        <v>129</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920278</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920278</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920449</v>
-      </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920449</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920449</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920279</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" t="s">
-        <v>131</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920279</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920279</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" t="s">
-        <v>131</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920447</v>
-      </c>
-      <c r="B42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" t="s">
-        <v>105</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920447</v>
-      </c>
-      <c r="B43" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" t="s">
-        <v>105</v>
-      </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920447</v>
-      </c>
-      <c r="B44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" t="s">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920284</v>
-      </c>
-      <c r="B45" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" t="s">
-        <v>133</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920284</v>
-      </c>
-      <c r="B46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920284</v>
-      </c>
-      <c r="B47" t="s">
-        <v>76</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>133</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920286</v>
-      </c>
-      <c r="B48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920286</v>
-      </c>
-      <c r="B49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>134</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920286</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>107</v>
-      </c>
-      <c r="D50" t="s">
-        <v>134</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920286</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" t="s">
-        <v>134</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>18330051920336</v>
-      </c>
-      <c r="B52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>18330051920336</v>
-      </c>
-      <c r="B53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" t="s">
-        <v>135</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>18330051920336</v>
-      </c>
-      <c r="B54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" t="s">
-        <v>135</v>
-      </c>
-      <c r="E54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920287</v>
-      </c>
-      <c r="B55" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55" t="s">
-        <v>136</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920287</v>
-      </c>
-      <c r="B56" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" t="s">
-        <v>109</v>
-      </c>
-      <c r="D56" t="s">
-        <v>136</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920287</v>
-      </c>
-      <c r="B57" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D57" t="s">
-        <v>136</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920289</v>
-      </c>
-      <c r="B58" t="s">
-        <v>80</v>
-      </c>
-      <c r="C58" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920289</v>
-      </c>
-      <c r="B59" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" t="s">
-        <v>137</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920289</v>
-      </c>
-      <c r="B60" t="s">
-        <v>80</v>
-      </c>
-      <c r="C60" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" t="s">
-        <v>137</v>
-      </c>
-      <c r="E60" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920343</v>
-      </c>
-      <c r="B61" t="s">
-        <v>81</v>
-      </c>
-      <c r="C61" t="s">
-        <v>76</v>
-      </c>
-      <c r="D61" t="s">
-        <v>138</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920343</v>
-      </c>
-      <c r="B62" t="s">
-        <v>81</v>
-      </c>
-      <c r="C62" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" t="s">
-        <v>138</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920343</v>
-      </c>
-      <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D63" t="s">
-        <v>138</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920292</v>
-      </c>
-      <c r="B64" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" t="s">
-        <v>139</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920292</v>
-      </c>
-      <c r="B65" t="s">
-        <v>82</v>
-      </c>
-      <c r="C65" t="s">
-        <v>72</v>
-      </c>
-      <c r="D65" t="s">
-        <v>139</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920292</v>
-      </c>
-      <c r="B66" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" t="s">
-        <v>139</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920293</v>
-      </c>
-      <c r="B67" t="s">
-        <v>83</v>
-      </c>
-      <c r="C67" t="s">
-        <v>111</v>
-      </c>
-      <c r="D67" t="s">
-        <v>140</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920293</v>
-      </c>
-      <c r="B68" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" t="s">
-        <v>140</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920293</v>
-      </c>
-      <c r="B69" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D69" t="s">
-        <v>140</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920294</v>
-      </c>
-      <c r="B70" t="s">
-        <v>84</v>
-      </c>
-      <c r="C70" t="s">
-        <v>64</v>
-      </c>
-      <c r="D70" t="s">
-        <v>141</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920294</v>
-      </c>
-      <c r="B71" t="s">
-        <v>84</v>
-      </c>
-      <c r="C71" t="s">
-        <v>64</v>
-      </c>
-      <c r="D71" t="s">
-        <v>141</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920294</v>
-      </c>
-      <c r="B72" t="s">
-        <v>84</v>
-      </c>
-      <c r="C72" t="s">
-        <v>64</v>
-      </c>
-      <c r="D72" t="s">
-        <v>141</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920296</v>
-      </c>
-      <c r="B73" t="s">
-        <v>85</v>
-      </c>
-      <c r="C73" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" t="s">
-        <v>142</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920296</v>
-      </c>
-      <c r="B74" t="s">
-        <v>85</v>
-      </c>
-      <c r="C74" t="s">
-        <v>112</v>
-      </c>
-      <c r="D74" t="s">
-        <v>142</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920296</v>
-      </c>
-      <c r="B75" t="s">
-        <v>85</v>
-      </c>
-      <c r="C75" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" t="s">
-        <v>142</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920295</v>
-      </c>
-      <c r="B76" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" t="s">
-        <v>113</v>
-      </c>
-      <c r="D76" t="s">
-        <v>143</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920295</v>
-      </c>
-      <c r="B77" t="s">
-        <v>85</v>
-      </c>
-      <c r="C77" t="s">
-        <v>113</v>
-      </c>
-      <c r="D77" t="s">
-        <v>143</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920295</v>
-      </c>
-      <c r="B78" t="s">
-        <v>85</v>
-      </c>
-      <c r="C78" t="s">
-        <v>113</v>
-      </c>
-      <c r="D78" t="s">
-        <v>143</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920297</v>
-      </c>
-      <c r="B79" t="s">
-        <v>86</v>
-      </c>
-      <c r="C79" t="s">
-        <v>81</v>
-      </c>
-      <c r="D79" t="s">
-        <v>144</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920297</v>
-      </c>
-      <c r="B80" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" t="s">
-        <v>144</v>
-      </c>
-      <c r="E80" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920297</v>
-      </c>
-      <c r="B81" t="s">
-        <v>86</v>
-      </c>
-      <c r="C81" t="s">
-        <v>81</v>
-      </c>
-      <c r="D81" t="s">
-        <v>144</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920298</v>
-      </c>
-      <c r="B82" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
-        <v>142</v>
-      </c>
-      <c r="E82" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920298</v>
-      </c>
-      <c r="B83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" t="s">
-        <v>142</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920298</v>
-      </c>
-      <c r="B84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" t="s">
-        <v>142</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920299</v>
-      </c>
-      <c r="B85" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" t="s">
-        <v>115</v>
-      </c>
-      <c r="D85" t="s">
-        <v>145</v>
-      </c>
-      <c r="E85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920299</v>
-      </c>
-      <c r="B86" t="s">
-        <v>88</v>
-      </c>
-      <c r="C86" t="s">
-        <v>115</v>
-      </c>
-      <c r="D86" t="s">
-        <v>145</v>
-      </c>
-      <c r="E86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920299</v>
-      </c>
-      <c r="B87" t="s">
-        <v>88</v>
-      </c>
-      <c r="C87" t="s">
-        <v>115</v>
-      </c>
-      <c r="D87" t="s">
-        <v>145</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920301</v>
-      </c>
-      <c r="B88" t="s">
-        <v>89</v>
-      </c>
-      <c r="C88" t="s">
-        <v>116</v>
-      </c>
-      <c r="D88" t="s">
-        <v>146</v>
-      </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920301</v>
-      </c>
-      <c r="B89" t="s">
-        <v>89</v>
-      </c>
-      <c r="C89" t="s">
-        <v>116</v>
-      </c>
-      <c r="D89" t="s">
-        <v>146</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920301</v>
-      </c>
-      <c r="B90" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" t="s">
-        <v>146</v>
-      </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920443</v>
-      </c>
-      <c r="B91" t="s">
-        <v>90</v>
-      </c>
-      <c r="C91" t="s">
-        <v>117</v>
-      </c>
-      <c r="D91" t="s">
-        <v>147</v>
-      </c>
-      <c r="E91" t="s">
-        <v>9</v>
-      </c>
-      <c r="F91" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920443</v>
-      </c>
-      <c r="B92" t="s">
-        <v>90</v>
-      </c>
-      <c r="C92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D92" t="s">
-        <v>147</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920443</v>
-      </c>
-      <c r="B93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" t="s">
-        <v>147</v>
-      </c>
-      <c r="E93" t="s">
-        <v>5</v>
-      </c>
-      <c r="F93" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920300</v>
-      </c>
-      <c r="B94" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" t="s">
-        <v>84</v>
-      </c>
-      <c r="D94" t="s">
-        <v>148</v>
-      </c>
-      <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920300</v>
-      </c>
-      <c r="B95" t="s">
-        <v>91</v>
-      </c>
-      <c r="C95" t="s">
-        <v>84</v>
-      </c>
-      <c r="D95" t="s">
-        <v>148</v>
-      </c>
-      <c r="E95" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920300</v>
-      </c>
-      <c r="B96" t="s">
-        <v>91</v>
-      </c>
-      <c r="C96" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" t="s">
-        <v>148</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920305</v>
-      </c>
-      <c r="B97" t="s">
-        <v>92</v>
-      </c>
-      <c r="C97" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" t="s">
-        <v>149</v>
-      </c>
-      <c r="E97" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920305</v>
-      </c>
-      <c r="B98" t="s">
-        <v>92</v>
-      </c>
-      <c r="C98" t="s">
-        <v>118</v>
-      </c>
-      <c r="D98" t="s">
-        <v>149</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920305</v>
-      </c>
-      <c r="B99" t="s">
-        <v>92</v>
-      </c>
-      <c r="C99" t="s">
-        <v>118</v>
-      </c>
-      <c r="D99" t="s">
-        <v>149</v>
-      </c>
-      <c r="E99" t="s">
-        <v>5</v>
-      </c>
-      <c r="F99" t="s">
         <v>55</v>
       </c>
     </row>
@@ -5625,546 +3774,546 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920269</v>
+        <v>18330051920319</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920273</v>
+        <v>19330051920269</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920286</v>
+        <v>19330051920273</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920270</v>
+        <v>19330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920272</v>
+        <v>19330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920268</v>
+        <v>19330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920274</v>
+        <v>19330051920268</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920242</v>
+        <v>19330051920274</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>17330051420245</v>
+        <v>18330051920242</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>18330051920321</v>
+        <v>17330051420245</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920278</v>
+        <v>18330051920321</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
         <v>129</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920449</v>
+        <v>19330051920278</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920279</v>
+        <v>19330051920449</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920447</v>
+        <v>19330051920279</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>132</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920284</v>
+        <v>19330051920447</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>18330051920336</v>
+        <v>19330051920284</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920287</v>
+        <v>18330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920289</v>
+        <v>19330051920287</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920343</v>
+        <v>19330051920289</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920292</v>
+        <v>19330051920343</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920293</v>
+        <v>19330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920294</v>
+        <v>19330051920293</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920296</v>
+        <v>19330051920294</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920295</v>
+        <v>19330051920296</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920297</v>
+        <v>19330051920295</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920298</v>
+        <v>19330051920297</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920299</v>
+        <v>19330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920301</v>
+        <v>19330051920299</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920443</v>
+        <v>19330051920301</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920300</v>
+        <v>19330051920443</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920305</v>
+        <v>19330051920300</v>
       </c>
       <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
         <v>92</v>
       </c>
-      <c r="C32" t="s">
-        <v>118</v>
-      </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>18330051920319</v>
+        <v>19330051920305</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6174,7 +4323,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6204,6 +4353,213 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920273</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920273</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920278</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920284</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>18330051920336</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920292</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920443</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -209,220 +209,220 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>DEGANTE</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>MANZANET</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
   </si>
   <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>BITHIA MARIAN</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
     <t>ELISA</t>
   </si>
   <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>SHARITH</t>
+    <t>BRENDA JANET</t>
+  </si>
+  <si>
+    <t>ADOLFO ANTONIO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>YOZELIN</t>
+  </si>
+  <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>AZAEL</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXIS</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
   </si>
   <si>
     <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>BITHIA MARIAN</t>
-  </si>
-  <si>
-    <t>IRIDIA</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>ADOLFO ANTONIO</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>YOZELIN</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>AZAEL</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>ANGEL ALEXIS</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
   </si>
   <si>
     <t>DIEGO OLLIN</t>
@@ -974,7 +974,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -986,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1022,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1045,13 +1045,13 @@
         <v>8</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1128,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1205,7 +1205,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1282,7 +1282,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1359,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1407,7 +1407,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1436,7 +1436,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1448,7 +1448,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1484,7 +1484,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1510,7 +1510,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1519,7 +1519,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1569,7 +1569,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1619,7 +1619,7 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1631,7 +1631,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1696,7 +1696,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1708,7 +1708,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1744,7 +1744,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1773,7 +1773,7 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1785,7 +1785,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1821,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1850,7 +1850,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1862,7 +1862,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1927,7 +1927,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1939,7 +1939,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1975,7 +1975,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2004,7 +2004,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2016,7 +2016,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2040,7 +2040,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2075,13 +2075,13 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2093,7 +2093,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2129,7 +2129,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2158,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2170,7 +2170,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2206,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2235,7 +2235,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2312,7 +2312,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2324,7 +2324,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2389,7 +2389,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2401,7 +2401,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2437,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2466,7 +2466,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2502,7 +2502,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2543,7 +2543,7 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2555,7 +2555,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2591,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2620,7 +2620,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2632,7 +2632,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2668,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2697,7 +2697,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2709,7 +2709,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2733,7 +2733,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2745,7 +2745,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2774,7 +2774,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2786,7 +2786,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2851,7 +2851,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2863,7 +2863,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2899,7 +2899,7 @@
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2928,7 +2928,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2940,7 +2940,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2964,7 +2964,7 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -2976,7 +2976,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3005,7 +3005,7 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3082,7 +3082,7 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3094,7 +3094,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3130,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3159,7 +3159,7 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3171,7 +3171,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3207,7 +3207,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3236,7 +3236,7 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3248,7 +3248,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3284,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3313,7 +3313,7 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3325,7 +3325,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3458,19 +3458,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3614,7 +3614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3643,16 +3643,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920269</v>
+        <v>19330051920273</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
         <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920273</v>
+        <v>18330051920319</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3686,59 +3686,19 @@
         <v>18330051920319</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>18330051920319</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3777,13 +3737,13 @@
         <v>18330051920319</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3791,16 +3751,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920269</v>
+        <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>71</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3808,47 +3768,47 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920273</v>
+        <v>19330051920270</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920286</v>
+        <v>19330051920272</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920270</v>
+        <v>19330051920269</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>123</v>
@@ -3859,13 +3819,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920272</v>
+        <v>19330051920268</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>124</v>
@@ -3876,13 +3836,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920268</v>
+        <v>19330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -3893,13 +3853,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920274</v>
+        <v>18330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
@@ -3910,13 +3870,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>18330051920242</v>
+        <v>17330051420245</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>127</v>
@@ -3927,13 +3887,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>17330051420245</v>
+        <v>18330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
@@ -3944,13 +3904,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>18330051920321</v>
+        <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
         <v>129</v>
@@ -3961,13 +3921,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920278</v>
+        <v>19330051920449</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
@@ -3978,13 +3938,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920449</v>
+        <v>19330051920279</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -3995,13 +3955,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920279</v>
+        <v>19330051920447</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
         <v>132</v>
@@ -4012,13 +3972,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920447</v>
+        <v>19330051920284</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -4029,13 +3989,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920284</v>
+        <v>19330051920286</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4049,10 +4009,10 @@
         <v>18330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -4066,10 +4026,10 @@
         <v>19330051920287</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -4083,10 +4043,10 @@
         <v>19330051920289</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4100,10 +4060,10 @@
         <v>19330051920343</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
         <v>138</v>
@@ -4117,10 +4077,10 @@
         <v>19330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>139</v>
@@ -4134,10 +4094,10 @@
         <v>19330051920293</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -4151,10 +4111,10 @@
         <v>19330051920294</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
         <v>141</v>
@@ -4168,10 +4128,10 @@
         <v>19330051920296</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
         <v>142</v>
@@ -4185,10 +4145,10 @@
         <v>19330051920295</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>143</v>
@@ -4202,10 +4162,10 @@
         <v>19330051920297</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
         <v>144</v>
@@ -4219,10 +4179,10 @@
         <v>19330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4236,10 +4196,10 @@
         <v>19330051920299</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4253,10 +4213,10 @@
         <v>19330051920301</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -4270,10 +4230,10 @@
         <v>19330051920443</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4287,10 +4247,10 @@
         <v>19330051920300</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4304,10 +4264,10 @@
         <v>19330051920305</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -4323,7 +4283,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4358,13 +4318,13 @@
         <v>19330051920273</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4381,13 +4341,13 @@
         <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4401,16 +4361,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920286</v>
+        <v>19330051920269</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4424,39 +4384,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920286</v>
+        <v>19330051920278</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920278</v>
+        <v>19330051920284</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4470,13 +4430,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920284</v>
+        <v>19330051920286</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
         <v>134</v>
@@ -4496,10 +4456,10 @@
         <v>18330051920336</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
         <v>135</v>
@@ -4516,47 +4476,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920292</v>
+        <v>19330051920443</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920443</v>
-      </c>
-      <c r="B10" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,10 +185,10 @@
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
+    <t>Rivera Serra Alma Lilian</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
@@ -971,19 +971,19 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>8</v>
@@ -1007,7 +1007,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1048,19 +1048,19 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1096,7 +1096,7 @@
         <v>6</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1125,19 +1125,19 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1202,19 +1202,19 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1279,19 +1279,19 @@
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1327,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>-1</v>
@@ -1356,19 +1356,19 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1404,7 +1404,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1433,19 +1433,19 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>6</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1481,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1507,16 +1507,16 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1537,7 +1537,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1557,7 +1557,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1584,7 +1584,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1616,19 +1616,19 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1652,7 +1652,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1664,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1693,19 +1693,19 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1729,7 +1729,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1741,7 +1741,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1770,19 +1770,19 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1806,19 +1806,19 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1847,19 +1847,19 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1924,19 +1924,19 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2001,19 +2001,19 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2049,7 +2049,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2078,19 +2078,19 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2114,7 +2114,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2126,7 +2126,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2155,19 +2155,19 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2232,19 +2232,19 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2268,19 +2268,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2309,19 +2309,19 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2386,19 +2386,19 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2422,13 +2422,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2463,19 +2463,19 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2499,19 +2499,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>7</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2540,19 +2540,19 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2576,13 +2576,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2617,19 +2617,19 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2653,7 +2653,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -2694,19 +2694,19 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2742,7 +2742,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2771,19 +2771,19 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2807,7 +2807,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2848,19 +2848,19 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2884,19 +2884,19 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>8</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2925,19 +2925,19 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -2961,19 +2961,19 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>9</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3002,22 +3002,22 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3038,13 +3038,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3053,7 +3053,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3079,19 +3079,19 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3127,7 +3127,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3156,19 +3156,19 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3233,19 +3233,19 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3269,7 +3269,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3281,7 +3281,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3310,19 +3310,19 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>9</v>
@@ -3426,19 +3426,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>77.42</v>
+        <v>70.97</v>
       </c>
       <c r="G2">
-        <v>19.35</v>
+        <v>25.81</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -3481,66 +3481,66 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>96.77</v>
+        <v>93.75</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>96.88</v>
+        <v>96.77</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
-        <v>3.13</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3554,19 +3554,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>96.77</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3614,7 +3614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3658,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3679,26 +3679,6 @@
       </c>
       <c r="F3" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>18330051920319</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3734,33 +3714,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>18330051920319</v>
+        <v>19330051920273</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920273</v>
+        <v>18330051920319</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4353,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4453,22 +4433,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920336</v>
+        <v>19330051920292</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>

--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -209,187 +209,187 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>DEGANTE</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>BITHIA MARIAN</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
   </si>
   <si>
     <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>SHARITH</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>BITHIA MARIAN</t>
-  </si>
-  <si>
-    <t>IRIDIA</t>
-  </si>
-  <si>
-    <t>ELISA</t>
   </si>
   <si>
     <t>BRENDA JANET</t>
@@ -992,7 +992,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1001,16 +1001,16 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1069,7 +1069,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1078,10 +1078,10 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1146,7 +1146,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1232,10 +1232,10 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>8</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -1294,13 +1294,13 @@
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1309,16 +1309,16 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1377,7 +1377,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1386,16 +1386,16 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1454,7 +1454,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1463,10 +1463,10 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1525,22 +1525,22 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>9</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1578,7 +1578,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1637,7 +1637,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1646,16 +1646,16 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1664,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1714,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1723,16 +1723,16 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1741,10 +1741,10 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1791,7 +1791,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1800,10 +1800,10 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1877,10 +1877,10 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1945,7 +1945,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1954,16 +1954,16 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2022,7 +2022,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2031,10 +2031,10 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2049,10 +2049,10 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2099,7 +2099,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2108,16 +2108,16 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
         <v>8</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2176,7 +2176,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2185,10 +2185,10 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2247,13 +2247,13 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2262,10 +2262,10 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2283,7 +2283,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2330,7 +2330,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2339,16 +2339,16 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2407,7 +2407,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2416,10 +2416,10 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2484,7 +2484,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2493,10 +2493,10 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2514,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2555,13 +2555,13 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2570,16 +2570,16 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2638,7 +2638,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2647,16 +2647,16 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2668,7 +2668,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2715,7 +2715,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2724,10 +2724,10 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2792,7 +2792,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2801,10 +2801,10 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2869,7 +2869,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2878,10 +2878,10 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2946,7 +2946,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2955,16 +2955,16 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2973,7 +2973,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3023,7 +3023,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3032,10 +3032,10 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3109,16 +3109,16 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>9</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3130,7 +3130,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3177,7 +3177,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3186,10 +3186,10 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3254,7 +3254,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3263,16 +3263,16 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>10</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3331,7 +3331,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3340,10 +3340,10 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3470,7 +3470,7 @@
         <v>6.25</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3525,22 +3525,22 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>96.77</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="H5">
         <v>8.1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3614,7 +3614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3643,41 +3643,21 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920273</v>
+        <v>18330051920319</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>18330051920319</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3714,16 +3694,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920273</v>
+        <v>18330051920319</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3731,30 +3711,30 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>18330051920319</v>
+        <v>19330051920270</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920270</v>
+        <v>19330051920272</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
         <v>121</v>
@@ -3765,13 +3745,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920272</v>
+        <v>19330051920269</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
         <v>122</v>
@@ -3782,13 +3762,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920269</v>
+        <v>19330051920273</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
         <v>123</v>
@@ -3802,10 +3782,10 @@
         <v>19330051920268</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
         <v>124</v>
@@ -3819,10 +3799,10 @@
         <v>19330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -3836,10 +3816,10 @@
         <v>18330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
@@ -3853,10 +3833,10 @@
         <v>17330051420245</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
         <v>127</v>
@@ -3870,10 +3850,10 @@
         <v>18330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
@@ -3887,10 +3867,10 @@
         <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>129</v>
@@ -3904,10 +3884,10 @@
         <v>19330051920449</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
@@ -3921,10 +3901,10 @@
         <v>19330051920279</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -3938,10 +3918,10 @@
         <v>19330051920447</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
         <v>132</v>
@@ -3955,10 +3935,10 @@
         <v>19330051920284</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3972,10 +3952,10 @@
         <v>19330051920286</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -3989,10 +3969,10 @@
         <v>18330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -4006,10 +3986,10 @@
         <v>19330051920287</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -4023,10 +4003,10 @@
         <v>19330051920289</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4040,10 +4020,10 @@
         <v>19330051920343</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>138</v>
@@ -4057,10 +4037,10 @@
         <v>19330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
         <v>139</v>
@@ -4074,10 +4054,10 @@
         <v>19330051920293</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -4091,10 +4071,10 @@
         <v>19330051920294</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
         <v>141</v>
@@ -4108,10 +4088,10 @@
         <v>19330051920296</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
         <v>142</v>
@@ -4125,10 +4105,10 @@
         <v>19330051920295</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>143</v>
@@ -4142,10 +4122,10 @@
         <v>19330051920297</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
         <v>144</v>
@@ -4159,10 +4139,10 @@
         <v>19330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4176,10 +4156,10 @@
         <v>19330051920299</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4193,10 +4173,10 @@
         <v>19330051920301</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -4210,10 +4190,10 @@
         <v>19330051920443</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4227,10 +4207,10 @@
         <v>19330051920300</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4244,10 +4224,10 @@
         <v>19330051920305</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -4263,7 +4243,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4295,16 +4275,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920273</v>
+        <v>19330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4321,36 +4301,36 @@
         <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920269</v>
+        <v>19330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4364,16 +4344,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920278</v>
+        <v>19330051920284</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4387,16 +4367,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920284</v>
+        <v>19330051920286</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
         <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4410,16 +4390,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920286</v>
+        <v>19330051920292</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -4433,16 +4413,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920292</v>
+        <v>19330051920443</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4451,29 +4431,6 @@
         <v>53</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920443</v>
-      </c>
-      <c r="B9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -998,7 +998,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1075,7 +1075,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -1093,7 +1093,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1152,7 +1152,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1229,7 +1229,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1306,7 +1306,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
@@ -1383,7 +1383,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1460,7 +1460,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1528,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1643,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -1720,7 +1720,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1738,7 +1738,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1797,7 +1797,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1874,7 +1874,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -2028,7 +2028,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -2123,7 +2123,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2182,7 +2182,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>5</v>
@@ -2277,7 +2277,7 @@
         <v>5</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2336,7 +2336,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -2354,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2413,7 +2413,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2567,7 +2567,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2644,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>10</v>
@@ -2662,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2721,7 +2721,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2798,7 +2798,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2816,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2875,7 +2875,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2893,7 +2893,7 @@
         <v>10</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2952,7 +2952,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>8</v>
@@ -3029,7 +3029,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>10</v>
@@ -3106,7 +3106,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>10</v>
@@ -3124,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3183,7 +3183,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>10</v>
@@ -3260,7 +3260,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
@@ -3278,7 +3278,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3337,7 +3337,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3355,7 +3355,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/6ALCV - Estadisticos 20212.xlsx
+++ b/grupos/6ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -209,199 +209,199 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>DEGANTE</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>BITHIA MARIAN</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>BRENDA JANET</t>
+  </si>
+  <si>
+    <t>ADOLFO ANTONIO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>YOZELIN</t>
+  </si>
+  <si>
     <t>SHARITH</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>BITHIA MARIAN</t>
-  </si>
-  <si>
-    <t>IRIDIA</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>ADOLFO ANTONIO</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>YOZELIN</t>
   </si>
   <si>
     <t>JHOVANA</t>
@@ -989,13 +989,13 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -1066,13 +1066,13 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1084,13 +1084,13 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1143,13 +1143,13 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1220,13 +1220,13 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>10</v>
@@ -1297,13 +1297,13 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1315,13 +1315,13 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>9</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1374,13 +1374,13 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>10</v>
@@ -1451,13 +1451,13 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1522,7 +1522,7 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -1537,7 +1537,7 @@
         <v>9</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1563,25 +1563,25 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
         <v>4</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1590,7 +1590,7 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1634,13 +1634,13 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1711,13 +1711,13 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1735,7 +1735,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1788,13 +1788,13 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>10</v>
@@ -1812,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1865,13 +1865,13 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1942,13 +1942,13 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>10</v>
@@ -2019,13 +2019,13 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -2043,7 +2043,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2096,13 +2096,13 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>10</v>
@@ -2120,7 +2120,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2173,13 +2173,13 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2250,13 +2250,13 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>4</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2327,13 +2327,13 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -2351,7 +2351,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2404,13 +2404,13 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2422,13 +2422,13 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>10</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2481,13 +2481,13 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2505,7 +2505,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2558,13 +2558,13 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2635,13 +2635,13 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>10</v>
@@ -2659,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2712,13 +2712,13 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>10</v>
@@ -2736,7 +2736,7 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2789,13 +2789,13 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2807,7 +2807,7 @@
         <v>7</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2866,13 +2866,13 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2943,13 +2943,13 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>10</v>
@@ -2967,7 +2967,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3020,13 +3020,13 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>10</v>
@@ -3038,13 +3038,13 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3097,13 +3097,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -3115,13 +3115,13 @@
         <v>7</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3174,13 +3174,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3251,13 +3251,13 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3328,13 +3328,13 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>9</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3426,25 +3426,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>70.97</v>
+        <v>93.55</v>
       </c>
       <c r="G2">
-        <v>25.81</v>
+        <v>6.45</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3502,7 +3502,7 @@
         <v>6.25</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3614,7 +3614,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3639,26 +3639,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>18330051920319</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3694,30 +3674,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>18330051920319</v>
+        <v>19330051920270</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920270</v>
+        <v>19330051920272</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
         <v>120</v>
@@ -3728,13 +3708,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920272</v>
+        <v>19330051920269</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
         <v>121</v>
@@ -3745,13 +3725,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920269</v>
+        <v>19330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>122</v>
@@ -3762,13 +3742,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920273</v>
+        <v>19330051920268</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>123</v>
@@ -3779,13 +3759,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920268</v>
+        <v>19330051920274</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>124</v>
@@ -3796,13 +3776,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920274</v>
+        <v>18330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>125</v>
@@ -3813,13 +3793,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920242</v>
+        <v>17330051420245</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>126</v>
@@ -3830,13 +3810,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>17330051420245</v>
+        <v>18330051920319</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
         <v>127</v>
@@ -3850,10 +3830,10 @@
         <v>18330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
         <v>128</v>
@@ -3867,10 +3847,10 @@
         <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
         <v>129</v>
@@ -3884,10 +3864,10 @@
         <v>19330051920449</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
@@ -3901,10 +3881,10 @@
         <v>19330051920279</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -3918,10 +3898,10 @@
         <v>19330051920447</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
         <v>132</v>
@@ -3935,10 +3915,10 @@
         <v>19330051920284</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -3952,10 +3932,10 @@
         <v>19330051920286</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -3969,10 +3949,10 @@
         <v>18330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -3986,10 +3966,10 @@
         <v>19330051920287</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -4003,10 +3983,10 @@
         <v>19330051920289</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4020,10 +4000,10 @@
         <v>19330051920343</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
         <v>138</v>
@@ -4037,10 +4017,10 @@
         <v>19330051920292</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
         <v>139</v>
@@ -4054,10 +4034,10 @@
         <v>19330051920293</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -4071,10 +4051,10 @@
         <v>19330051920294</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
         <v>141</v>
@@ -4088,10 +4068,10 @@
         <v>19330051920296</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>142</v>
@@ -4105,10 +4085,10 @@
         <v>19330051920295</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>143</v>
@@ -4122,10 +4102,10 @@
         <v>19330051920297</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
         <v>144</v>
@@ -4139,10 +4119,10 @@
         <v>19330051920298</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4156,10 +4136,10 @@
         <v>19330051920299</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4173,10 +4153,10 @@
         <v>19330051920301</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -4190,10 +4170,10 @@
         <v>19330051920443</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4207,10 +4187,10 @@
         <v>19330051920300</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4224,10 +4204,10 @@
         <v>19330051920305</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D33" t="s">
         <v>149</v>
@@ -4243,7 +4223,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4273,167 +4253,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920269</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920273</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920278</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920284</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920286</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920292</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920443</v>
-      </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
